--- a/data/trans_bre/P8_2_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P8_2_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 10,4</t>
+          <t>-2,75; 9,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 17,23</t>
+          <t>4,29; 17,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 15,71</t>
+          <t>1,41; 16,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 10,36</t>
+          <t>-1,17; 9,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 86,91</t>
+          <t>-15,27; 78,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,29; 137,56</t>
+          <t>23,09; 132,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 103,94</t>
+          <t>4,85; 107,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 90,92</t>
+          <t>-4,94; 86,95</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 16,41</t>
+          <t>6,37; 15,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 15,89</t>
+          <t>5,79; 16,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 14,52</t>
+          <t>5,02; 14,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 10,9</t>
+          <t>1,22; 10,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,17; 147,7</t>
+          <t>41,07; 142,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,77; 128,44</t>
+          <t>30,3; 131,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,81; 145,41</t>
+          <t>35,15; 148,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 68,39</t>
+          <t>4,91; 70,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 19,53</t>
+          <t>8,56; 19,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 13,2</t>
+          <t>0,84; 13,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 11,92</t>
+          <t>0,11; 11,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 9,45</t>
+          <t>0,25; 9,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,35; 214,25</t>
+          <t>60,04; 228,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 100,35</t>
+          <t>3,79; 100,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 110,45</t>
+          <t>-0,76; 108,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 78,71</t>
+          <t>1,34; 86,74</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 16,14</t>
+          <t>5,05; 16,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 21,68</t>
+          <t>9,42; 21,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 17,72</t>
+          <t>5,25; 17,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 5,69</t>
+          <t>-9,01; 5,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,39; 155,86</t>
+          <t>33,71; 164,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,3; 171,14</t>
+          <t>49,63; 169,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,24; 137,57</t>
+          <t>28,03; 132,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,13; 36,63</t>
+          <t>-43,08; 33,26</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 16,18</t>
+          <t>2,88; 16,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 21,58</t>
+          <t>5,27; 22,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 15,95</t>
+          <t>2,28; 16,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 16,6</t>
+          <t>-1,01; 16,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,06; 245,89</t>
+          <t>21,34; 250,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,77; 168,64</t>
+          <t>23,37; 171,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,88; 167,97</t>
+          <t>8,17; 167,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 160,41</t>
+          <t>-5,73; 163,12</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 17,52</t>
+          <t>3,38; 16,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 15,06</t>
+          <t>1,53; 15,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 17,04</t>
+          <t>2,62; 17,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,35</t>
+          <t>2,17; 11,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,75; 149,01</t>
+          <t>16,17; 137,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 91,82</t>
+          <t>5,76; 91,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,48; 101,68</t>
+          <t>10,98; 102,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,86; 107,68</t>
+          <t>14,39; 112,15</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 11,84</t>
+          <t>3,4; 11,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 17,06</t>
+          <t>8,07; 16,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 11,55</t>
+          <t>2,6; 11,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 9,76</t>
+          <t>-8,08; 9,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,81; 87,32</t>
+          <t>18,39; 87,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,8; 155,24</t>
+          <t>52,81; 155,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,24; 83,03</t>
+          <t>12,27; 79,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 62,08</t>
+          <t>-42,21; 64,0</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,96; 12,84</t>
+          <t>4,76; 12,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,97</t>
+          <t>2,06; 10,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,96; 11,42</t>
+          <t>3,66; 11,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 12,2</t>
+          <t>-47,22; 12,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,0; 102,78</t>
+          <t>27,79; 100,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,06; 73,8</t>
+          <t>11,02; 71,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,66; 111,31</t>
+          <t>25,5; 101,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 99,75</t>
+          <t>-66,42; 99,28</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,12</t>
+          <t>7,27; 11,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,09</t>
+          <t>8,19; 12,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,14</t>
+          <t>6,48; 10,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 6,48</t>
+          <t>-17,84; 6,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50,68; 84,71</t>
+          <t>48,79; 84,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,81; 82,53</t>
+          <t>50,46; 83,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,05; 73,47</t>
+          <t>42,13; 76,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 42,99</t>
+          <t>-46,99; 44,65</t>
         </is>
       </c>
     </row>
